--- a/template/8.19/净值.xlsx
+++ b/template/8.19/净值.xlsx
@@ -1033,7 +1033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E127"/>
+  <dimension ref="A1:E129"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -3948,18 +3948,64 @@
           <t>2025/08/19</t>
         </is>
       </c>
-      <c r="B127" t="n">
+      <c r="B127" s="0" t="n">
         <v>0.99343</v>
       </c>
-      <c r="C127" t="inlineStr">
+      <c r="C127" s="0" t="inlineStr">
         <is>
           <t>-0.661%</t>
         </is>
       </c>
-      <c r="D127" t="n">
+      <c r="D127" s="0" t="n">
         <v>0.98689</v>
       </c>
-      <c r="E127" t="inlineStr">
+      <c r="E127" s="0" t="inlineStr">
+        <is>
+          <t>-1.3148%</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/19</t>
+        </is>
+      </c>
+      <c r="B128" s="0" t="n">
+        <v>0.99343</v>
+      </c>
+      <c r="C128" s="0" t="inlineStr">
+        <is>
+          <t>-0.661%</t>
+        </is>
+      </c>
+      <c r="D128" s="0" t="n">
+        <v>0.98689</v>
+      </c>
+      <c r="E128" s="0" t="inlineStr">
+        <is>
+          <t>-1.3148%</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/19</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>0.99343</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>-0.661%</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>0.98689</v>
+      </c>
+      <c r="E129" t="inlineStr">
         <is>
           <t>-1.3148%</t>
         </is>
@@ -3977,7 +4023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E127"/>
+  <dimension ref="A1:E129"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -6892,18 +6938,64 @@
           <t>2025/08/19</t>
         </is>
       </c>
-      <c r="B127" t="n">
+      <c r="B127" s="0" t="n">
         <v>0.99466</v>
       </c>
-      <c r="C127" t="inlineStr">
+      <c r="C127" s="0" t="inlineStr">
         <is>
           <t>-0.5383%</t>
         </is>
       </c>
-      <c r="D127" t="n">
+      <c r="D127" s="0" t="n">
         <v>0.98812</v>
       </c>
-      <c r="E127" t="inlineStr">
+      <c r="E127" s="0" t="inlineStr">
+        <is>
+          <t>-1.1922%</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/19</t>
+        </is>
+      </c>
+      <c r="B128" s="0" t="n">
+        <v>0.99466</v>
+      </c>
+      <c r="C128" s="0" t="inlineStr">
+        <is>
+          <t>-0.5383%</t>
+        </is>
+      </c>
+      <c r="D128" s="0" t="n">
+        <v>0.98812</v>
+      </c>
+      <c r="E128" s="0" t="inlineStr">
+        <is>
+          <t>-1.1922%</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/19</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>0.99466</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>-0.5383%</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>0.98812</v>
+      </c>
+      <c r="E129" t="inlineStr">
         <is>
           <t>-1.1922%</t>
         </is>
@@ -6921,7 +7013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E110"/>
+  <dimension ref="A1:E112"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -9447,18 +9539,64 @@
           <t>2025/08/19</t>
         </is>
       </c>
-      <c r="B110" t="n">
+      <c r="B110" s="0" t="n">
         <v>0.99121</v>
       </c>
-      <c r="C110" t="inlineStr">
+      <c r="C110" s="0" t="inlineStr">
         <is>
           <t>-3.2111%</t>
         </is>
       </c>
-      <c r="D110" t="n">
+      <c r="D110" s="0" t="n">
         <v>0.98743</v>
       </c>
-      <c r="E110" t="inlineStr">
+      <c r="E110" s="0" t="inlineStr">
+        <is>
+          <t>-3.5587%</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/19</t>
+        </is>
+      </c>
+      <c r="B111" s="0" t="n">
+        <v>0.99121</v>
+      </c>
+      <c r="C111" s="0" t="inlineStr">
+        <is>
+          <t>-3.2111%</t>
+        </is>
+      </c>
+      <c r="D111" s="0" t="n">
+        <v>0.98743</v>
+      </c>
+      <c r="E111" s="0" t="inlineStr">
+        <is>
+          <t>-3.5587%</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/19</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>0.99121</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>-3.2111%</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>0.98743</v>
+      </c>
+      <c r="E112" t="inlineStr">
         <is>
           <t>-3.5587%</t>
         </is>
@@ -9475,7 +9613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E110"/>
+  <dimension ref="A1:E112"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -12001,18 +12139,64 @@
           <t>2025/08/19</t>
         </is>
       </c>
-      <c r="B110" t="n">
+      <c r="B110" s="0" t="n">
         <v>0.9902</v>
       </c>
-      <c r="C110" t="inlineStr">
+      <c r="C110" s="0" t="inlineStr">
         <is>
           <t>-3.7075%</t>
         </is>
       </c>
-      <c r="D110" t="n">
+      <c r="D110" s="0" t="n">
         <v>0.98642</v>
       </c>
-      <c r="E110" t="inlineStr">
+      <c r="E110" s="0" t="inlineStr">
+        <is>
+          <t>-4.0539%</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/19</t>
+        </is>
+      </c>
+      <c r="B111" s="0" t="n">
+        <v>0.9902</v>
+      </c>
+      <c r="C111" s="0" t="inlineStr">
+        <is>
+          <t>-3.7075%</t>
+        </is>
+      </c>
+      <c r="D111" s="0" t="n">
+        <v>0.98642</v>
+      </c>
+      <c r="E111" s="0" t="inlineStr">
+        <is>
+          <t>-4.0539%</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/19</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>0.9902</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>-3.7075%</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>0.98642</v>
+      </c>
+      <c r="E112" t="inlineStr">
         <is>
           <t>-4.0539%</t>
         </is>
@@ -12030,7 +12214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -13314,18 +13498,64 @@
           <t>2025/08/19</t>
         </is>
       </c>
-      <c r="B56" t="n">
+      <c r="B56" s="0" t="n">
         <v>0.99098</v>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="0" t="inlineStr">
         <is>
           <t>-0.9815%</t>
         </is>
       </c>
-      <c r="D56" t="n">
+      <c r="D56" s="0" t="n">
         <v>0.98809</v>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E56" s="0" t="inlineStr">
+        <is>
+          <t>-1.2582%</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/19</t>
+        </is>
+      </c>
+      <c r="B57" s="0" t="n">
+        <v>0.99098</v>
+      </c>
+      <c r="C57" s="0" t="inlineStr">
+        <is>
+          <t>-0.9815%</t>
+        </is>
+      </c>
+      <c r="D57" s="0" t="n">
+        <v>0.98809</v>
+      </c>
+      <c r="E57" s="0" t="inlineStr">
+        <is>
+          <t>-1.2582%</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/19</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>0.99098</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>-0.9815%</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>0.98809</v>
+      </c>
+      <c r="E58" t="inlineStr">
         <is>
           <t>-1.2582%</t>
         </is>
@@ -13342,7 +13572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -14626,18 +14856,64 @@
           <t>2025/08/19</t>
         </is>
       </c>
-      <c r="B56" t="n">
+      <c r="B56" s="0" t="n">
         <v>0.9909</v>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="0" t="inlineStr">
         <is>
           <t>-0.9888%</t>
         </is>
       </c>
-      <c r="D56" t="n">
+      <c r="D56" s="0" t="n">
         <v>0.98802</v>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E56" s="0" t="inlineStr">
+        <is>
+          <t>-1.2655%</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/19</t>
+        </is>
+      </c>
+      <c r="B57" s="0" t="n">
+        <v>0.9909</v>
+      </c>
+      <c r="C57" s="0" t="inlineStr">
+        <is>
+          <t>-0.9888%</t>
+        </is>
+      </c>
+      <c r="D57" s="0" t="n">
+        <v>0.98802</v>
+      </c>
+      <c r="E57" s="0" t="inlineStr">
+        <is>
+          <t>-1.2655%</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/19</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>0.9909</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>-0.9888%</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>0.98802</v>
+      </c>
+      <c r="E58" t="inlineStr">
         <is>
           <t>-1.2655%</t>
         </is>
